--- a/pengurus.xlsx
+++ b/pengurus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fatha\Downloads\HTML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AADA557-6AAA-447B-84E4-396DC58F39D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AA077BF-BC83-41D9-B670-54B2DEEF7111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F963CA3B-89AF-46AC-A632-BCEAD7CD37E4}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="168">
   <si>
     <t>Nama</t>
   </si>
@@ -525,6 +525,24 @@
   </si>
   <si>
     <t>Wakil Ketua II</t>
+  </si>
+  <si>
+    <t>50.</t>
+  </si>
+  <si>
+    <t>Gea Aulia Ramadhani</t>
+  </si>
+  <si>
+    <t>17 tahun</t>
+  </si>
+  <si>
+    <t>51.</t>
+  </si>
+  <si>
+    <t>Muhammad Rayvan Ridwan</t>
+  </si>
+  <si>
+    <t>20 tahun</t>
   </si>
 </sst>
 </file>
@@ -2028,12 +2046,44 @@
       </c>
     </row>
     <row r="51" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="6"/>
-      <c r="F51" s="2"/>
+      <c r="A51" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="6"/>
-      <c r="F52" s="2"/>
+      <c r="A52" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
